--- a/docs/Decodifiche/165_dmnm_dec_tipo_cittadinanza.xlsx
+++ b/docs/Decodifiche/165_dmnm_dec_tipo_cittadinanza.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>ITALIANA - PER NASCITA</t>
   </si>
   <si>
-    <t>2025-12-02 20:24:12.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>NON CONOSCIUTA</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:24:13.0</t>
   </si>
 </sst>
 </file>
@@ -204,7 +201,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
